--- a/utils/monday_sprint_sprint_2023-03.xlsx
+++ b/utils/monday_sprint_sprint_2023-03.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="152">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>16656</t>
+    <t>3612029044</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>02/12/2022</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>11/02/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>17715</t>
+    <t>3736149237</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -114,10 +114,13 @@
     <t>02/01/2023</t>
   </si>
   <si>
+    <t>09/02/2023</t>
+  </si>
+  <si>
     <t>Janeiro</t>
   </si>
   <si>
-    <t>18026</t>
+    <t>3822018630</t>
   </si>
   <si>
     <t>Alterar a ordem da denominação dos desenhos</t>
@@ -129,10 +132,13 @@
     <t>17/01/2023</t>
   </si>
   <si>
+    <t>04/02/2023</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
-    <t>18085</t>
+    <t>3839954925</t>
   </si>
   <si>
     <t>Correção no Sistema de Apontamento de Inspeção</t>
@@ -144,7 +150,7 @@
     <t>19/01/2023</t>
   </si>
   <si>
-    <t>18058</t>
+    <t>3843818271</t>
   </si>
   <si>
     <t>Vincular proforma a operação debit memo</t>
@@ -153,7 +159,10 @@
     <t>20/01/2023</t>
   </si>
   <si>
-    <t>12162</t>
+    <t>08/02/2023</t>
+  </si>
+  <si>
+    <t>3856495228</t>
   </si>
   <si>
     <t>Melhoria na movimentação agrupada com o setor 8886 (Envio de peças usinagem)</t>
@@ -165,43 +174,46 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>18000</t>
+    <t>3856556033</t>
   </si>
   <si>
     <t>Alteração do relatório de CVM conforme Distribuição do Saldo do Deposito</t>
   </si>
   <si>
-    <t>18038</t>
+    <t>06/02/2023</t>
+  </si>
+  <si>
+    <t>3856596135</t>
   </si>
   <si>
     <t>Identificação de Devolução de Venda no Estorno de Sequencia</t>
   </si>
   <si>
-    <t>18040</t>
+    <t>3856653250</t>
   </si>
   <si>
     <t>Alteração no layout da tela de geração de etiquetas para depósito/usinagem</t>
   </si>
   <si>
-    <t>18060</t>
+    <t>3856697054</t>
   </si>
   <si>
     <t>Ajuste no sistema de Proforma</t>
   </si>
   <si>
-    <t>18079</t>
+    <t>3856732799</t>
   </si>
   <si>
     <t>Campo 3D pré-usinado no preenchimento da OTF</t>
   </si>
   <si>
-    <t>18100</t>
+    <t>3856752338</t>
   </si>
   <si>
     <t>Nome do comprador no relatório de OCs emitidas</t>
   </si>
   <si>
-    <t>18139</t>
+    <t>3883080435</t>
   </si>
   <si>
     <t>itens movimentados para o setor 9995 no MPS diário</t>
@@ -210,81 +222,87 @@
     <t>27/01/2023</t>
   </si>
   <si>
-    <t>18162</t>
+    <t>3883141068</t>
   </si>
   <si>
     <t>Remoção de campos da tela de Estrutura MRP</t>
   </si>
   <si>
-    <t>18276</t>
+    <t>02/02/2023</t>
+  </si>
+  <si>
+    <t>3885062513</t>
   </si>
   <si>
     <t>Botão para abrir FTU em formato PDF</t>
   </si>
   <si>
-    <t>18292</t>
+    <t>3885846900</t>
   </si>
   <si>
     <t>Relacionar duplicatas do Benner com as notas fiscais do processo de exportação;</t>
   </si>
   <si>
-    <t>18296</t>
+    <t>31/01/2023</t>
+  </si>
+  <si>
+    <t>3885872253</t>
   </si>
   <si>
     <t>Integrar ordens de compra com o Sistema Benner</t>
   </si>
   <si>
-    <t>18297</t>
+    <t>3886014597</t>
   </si>
   <si>
     <t>Controle de paradas no apontamento de acabamento</t>
   </si>
   <si>
-    <t>18168</t>
+    <t>3886072010</t>
   </si>
   <si>
     <t>Proformas com revisão de valores</t>
   </si>
   <si>
-    <t>18222</t>
+    <t>30/01/2023</t>
+  </si>
+  <si>
+    <t>3886109134</t>
   </si>
   <si>
     <t>Inclusão de coluna no relatório de Invoices</t>
   </si>
   <si>
-    <t>18178</t>
+    <t>3886136564</t>
   </si>
   <si>
     <t>Preenchimento obrigatório no campo de responsável na tela de parecer de consertos</t>
   </si>
   <si>
-    <t>18251</t>
+    <t>3886143483</t>
   </si>
   <si>
     <t>Inclusão de setor no fluxo de produção</t>
   </si>
   <si>
-    <t>18186</t>
+    <t>3886157864</t>
   </si>
   <si>
     <t>Novas alterações no fluxo pré-produtivo</t>
   </si>
   <si>
-    <t>18301</t>
+    <t>3886283581</t>
   </si>
   <si>
     <t>Desenvolver uma funcionalidade de pausa ou medir separadamente o tempo de cura na moldagem USE/ULE</t>
   </si>
   <si>
-    <t>18311</t>
+    <t>3893611159</t>
   </si>
   <si>
     <t>Correções no processo de SIC</t>
   </si>
   <si>
-    <t>30/01/2023</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -300,12 +318,18 @@
     <t>Não definida</t>
   </si>
   <si>
+    <t>12/02/2023</t>
+  </si>
+  <si>
     <t>3895549581</t>
   </si>
   <si>
     <t>3895549668</t>
   </si>
   <si>
+    <t>3912120914</t>
+  </si>
+  <si>
     <t>Criar campos para atender 3D pre-usinado</t>
   </si>
   <si>
@@ -315,30 +339,27 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>18429</t>
+    <t>3919398515</t>
   </si>
   <si>
     <t>Melhorias apontamento de moldagem USE/ULE</t>
   </si>
   <si>
-    <t>02/02/2023</t>
-  </si>
-  <si>
-    <t>18430</t>
+    <t>3919683328</t>
   </si>
   <si>
     <t>Alerta por e-mail quando tempo de apontamento for maior que o da FTF</t>
   </si>
   <si>
-    <t>18453</t>
+    <t>07/02/2023</t>
+  </si>
+  <si>
+    <t>3945748880</t>
   </si>
   <si>
     <t>Relatório de fretes FOB e especiais</t>
   </si>
   <si>
-    <t>07/02/2023</t>
-  </si>
-  <si>
     <t>3964687790</t>
   </si>
   <si>
@@ -366,7 +387,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-03</t>
+    <t>Dez/2022</t>
   </si>
   <si>
     <t>Base</t>
@@ -1008,7 +1029,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1020,12 +1041,12 @@
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1037,13 +1058,13 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -1052,10 +1073,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1064,15 +1085,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1084,13 +1105,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1099,7 +1120,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1111,15 +1132,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1131,13 +1152,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1146,10 +1167,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1158,15 +1179,15 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1178,10 +1199,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1193,11 +1214,11 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1205,15 +1226,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1225,25 +1246,25 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1252,15 +1273,15 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1272,13 +1293,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1287,11 +1308,11 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
@@ -1299,15 +1320,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1319,13 +1340,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1334,11 +1355,11 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1346,15 +1367,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1366,13 +1387,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1381,11 +1402,11 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
       </c>
@@ -1393,15 +1414,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1413,10 +1434,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1428,10 +1449,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1440,15 +1461,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1460,10 +1481,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1475,10 +1496,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1487,15 +1508,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1507,10 +1528,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1522,10 +1543,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1534,15 +1555,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1554,10 +1575,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1569,10 +1590,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1581,15 +1602,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1601,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1616,10 +1637,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1628,15 +1649,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1648,13 +1669,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1663,10 +1684,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1675,15 +1696,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1695,13 +1716,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1710,10 +1731,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1722,15 +1743,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1742,13 +1763,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1757,7 +1778,7 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>24</v>
@@ -1769,15 +1790,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1789,10 +1810,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1804,10 +1825,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1816,15 +1837,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1836,10 +1857,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1851,10 +1872,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1863,15 +1884,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1883,10 +1904,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1898,10 +1919,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1910,15 +1931,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1930,10 +1951,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1945,7 +1966,7 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -1957,15 +1978,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1977,10 +1998,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1992,7 +2013,7 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>24</v>
@@ -2004,15 +2025,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2024,13 +2045,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2039,10 +2060,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2051,15 +2072,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2071,13 +2092,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2086,10 +2107,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2098,33 +2119,33 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2133,10 +2154,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2145,33 +2166,33 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2180,10 +2201,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2192,62 +2213,62 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="O29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2259,13 +2280,13 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2274,10 +2295,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2289,12 +2310,12 @@
         <v>27</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2306,10 +2327,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2321,10 +2342,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2336,12 +2357,12 @@
         <v>27</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2353,10 +2374,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2368,10 +2389,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2383,12 +2404,12 @@
         <v>27</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2400,13 +2421,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2415,10 +2436,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2430,12 +2451,12 @@
         <v>27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2447,13 +2468,13 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2462,10 +2483,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2474,15 +2495,15 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2494,13 +2515,13 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2509,10 +2530,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2521,10 +2542,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2540,23 +2561,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2564,16 +2585,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2584,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>13.88</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2592,7 +2613,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2605,7 +2626,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2613,7 +2634,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2644,12 +2665,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>34</v>
@@ -2663,7 +2684,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2673,25 +2694,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2708,13 +2729,13 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2729,7 +2750,7 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -2740,7 +2761,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -2752,51 +2773,51 @@
         <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="Q12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>20</v>
       </c>
@@ -2804,41 +2825,29 @@
         <v>15</v>
       </c>
       <c r="M13" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14">
-        <v>4</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2846,7 +2855,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2854,7 +2863,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2862,10 +2871,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2873,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2881,142 +2890,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2">
         <v>56</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
